--- a/data/trans_orig/DCD_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34171</t>
+          <t>34205</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59596</t>
+          <t>58185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78578</t>
+          <t>77581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108255</t>
+          <t>107798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118285</t>
+          <t>118969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157907</t>
+          <t>159229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445616</t>
+          <t>447027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471041</t>
+          <t>471007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339212</t>
+          <t>339669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368889</t>
+          <t>369886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794772</t>
+          <t>793450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834394</t>
+          <t>833710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>60943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77043</t>
+          <t>78572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103705</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120761</t>
+          <t>120695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159625</t>
+          <t>156827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391425</t>
+          <t>391270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416891</t>
+          <t>415182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278875</t>
+          <t>277162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305537</t>
+          <t>304008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675168</t>
+          <t>677966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714032</t>
+          <t>714098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113005</t>
+          <t>115162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67421</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>59489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183628</t>
+          <t>181672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555259</t>
+          <t>553102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642821</t>
+          <t>641950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99490</t>
+          <t>100549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119462</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651547</t>
+          <t>653503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>780816</t>
+          <t>775686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166792</t>
+          <t>164782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215332</t>
+          <t>213266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102595</t>
+          <t>112161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>255021</t>
+          <t>254349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273356</t>
+          <t>262870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437789</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>819487</t>
+          <t>821553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868027</t>
+          <t>870037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>723073</t>
+          <t>723745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>875499</t>
+          <t>865933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1575123</t>
+          <t>1578478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1739556</t>
+          <t>1750042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77506</t>
+          <t>77943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112247</t>
+          <t>111379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196013</t>
+          <t>208668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>313675</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>302004</t>
+          <t>298382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>405576</t>
+          <t>405512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>362799</t>
+          <t>363667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>397540</t>
+          <t>397103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527660</t>
+          <t>526980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>645322</t>
+          <t>632667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>910805</t>
+          <t>910869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1014377</t>
+          <t>1017999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201137</t>
+          <t>204010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246847</t>
+          <t>247749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>205766</t>
+          <t>205605</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>256290</t>
+          <t>259288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224593</t>
+          <t>224100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237085</t>
+          <t>237166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>514524</t>
+          <t>513622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>560234</t>
+          <t>557361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>745588</t>
+          <t>742590</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>796112</t>
+          <t>796273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>344292</t>
+          <t>352556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>501579</t>
+          <t>499834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>754247</t>
+          <t>756796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1014569</t>
+          <t>1012035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1209785</t>
+          <t>1195890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1493355</t>
+          <t>1485211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2874481</t>
+          <t>2876226</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3031768</t>
+          <t>3023504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2563189</t>
+          <t>2565723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2823511</t>
+          <t>2820962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5460463</t>
+          <t>5468607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5744033</t>
+          <t>5757928</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45773</t>
+          <t>50333</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>102855</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77581</t>
+          <t>87458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>119771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>138053</t>
+          <t>153188</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118969</t>
+          <t>133103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159229</t>
+          <t>175631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>459439</t>
+          <t>500285</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447027</t>
+          <t>485834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471007</t>
+          <t>513046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>355187</t>
+          <t>385556</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339669</t>
+          <t>368640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369886</t>
+          <t>400953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>814626</t>
+          <t>885841</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>793450</t>
+          <t>863398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>833710</t>
+          <t>905926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>49106</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60943</t>
+          <t>62450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78572</t>
+          <t>90409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>138079</t>
+          <t>152786</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120695</t>
+          <t>133756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156827</t>
+          <t>175510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>404344</t>
+          <t>434106</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391270</t>
+          <t>420762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415182</t>
+          <t>446471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>292370</t>
+          <t>319463</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277162</t>
+          <t>303167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>304008</t>
+          <t>332734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>696714</t>
+          <t>753569</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677966</t>
+          <t>730845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714098</t>
+          <t>772599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>75354</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115162</t>
+          <t>92789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>64002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66362</t>
+          <t>75262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>125429</t>
+          <t>139356</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59489</t>
+          <t>121538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181672</t>
+          <t>159368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>600299</t>
+          <t>396258</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553102</t>
+          <t>378823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641950</t>
+          <t>411858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109447</t>
+          <t>123495</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100549</t>
+          <t>112235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119891</t>
+          <t>133783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>709746</t>
+          <t>519753</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653503</t>
+          <t>499741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>775686</t>
+          <t>537571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>188212</t>
+          <t>201474</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164782</t>
+          <t>176933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213266</t>
+          <t>230614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>194198</t>
+          <t>218712</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112161</t>
+          <t>196837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254349</t>
+          <t>241942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>382410</t>
+          <t>420186</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262870</t>
+          <t>385679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>434434</t>
+          <t>456282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>846607</t>
+          <t>930369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>821553</t>
+          <t>901229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870037</t>
+          <t>954910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>783896</t>
+          <t>642499</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>723745</t>
+          <t>619269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>865933</t>
+          <t>664374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1630502</t>
+          <t>1572868</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1578478</t>
+          <t>1536772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1750042</t>
+          <t>1607375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>93487</t>
+          <t>99197</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77943</t>
+          <t>81914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111379</t>
+          <t>118728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>273279</t>
+          <t>296636</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208668</t>
+          <t>276533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>314355</t>
+          <t>321287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>366766</t>
+          <t>395833</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>298382</t>
+          <t>366307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>405512</t>
+          <t>426930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>381559</t>
+          <t>468767</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363667</t>
+          <t>449236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>397103</t>
+          <t>486050</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>568056</t>
+          <t>534214</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526980</t>
+          <t>509563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632667</t>
+          <t>554317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>949615</t>
+          <t>1002981</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>910869</t>
+          <t>971884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017999</t>
+          <t>1032507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>223551</t>
+          <t>242976</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>204010</t>
+          <t>219902</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247749</t>
+          <t>267715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>231382</t>
+          <t>250522</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>205605</t>
+          <t>222928</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>259288</t>
+          <t>276547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232676</t>
+          <t>229682</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224100</t>
+          <t>222237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237166</t>
+          <t>233957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>537820</t>
+          <t>601305</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>513622</t>
+          <t>576566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>557361</t>
+          <t>624379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>770496</t>
+          <t>830987</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>742590</t>
+          <t>804962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>796273</t>
+          <t>858581</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>451137</t>
+          <t>483010</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>352556</t>
+          <t>444586</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>499834</t>
+          <t>524676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>930982</t>
+          <t>1028860</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>756796</t>
+          <t>984546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1012035</t>
+          <t>1075406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1382119</t>
+          <t>1511870</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1195890</t>
+          <t>1451080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1485211</t>
+          <t>1576095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2924923</t>
+          <t>2959466</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2876226</t>
+          <t>2917800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3023504</t>
+          <t>2997890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2646776</t>
+          <t>2606533</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2565723</t>
+          <t>2559987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2820962</t>
+          <t>2650847</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5571699</t>
+          <t>5565999</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5468607</t>
+          <t>5501774</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5757928</t>
+          <t>5626789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
